--- a/products/Workforce Plan Template.xlsx
+++ b/products/Workforce Plan Template.xlsx
@@ -10,7 +10,9 @@
     <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Workforce Plan" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Workforce Plan'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="mmm d, yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +79,12 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="0033415C"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -127,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,6 +171,7 @@
     <xf numFmtId="166" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -649,6 +658,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0014213D"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -725,10 +735,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000F766E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1017,12 +1028,22 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>CPM Toolkit  |  Workforce Plan Template  |  v1.0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>